--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2323E15C-17C9-4463-9B6B-74E1D7C960C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1382D9C5-DE0B-4446-B9DA-5814B2B3E290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="214">
   <si>
     <t>type</t>
   </si>
@@ -565,12 +565,6 @@
   </si>
   <si>
     <t>Ce code a déjà été sélectionné.</t>
-  </si>
-  <si>
-    <t>. = 'FATICK' or . = 'KHOMBOLE'</t>
-  </si>
-  <si>
-    <t>Fatick et Khombole uniquement</t>
   </si>
   <si>
     <t>${q_autre_nom_1} nombre d'oeufs lame A</t>
@@ -1504,7 +1498,7 @@
       <c r="S3" s="16"/>
       <c r="T3" s="16"/>
     </row>
-    <row r="4" spans="1:20" s="5" customFormat="1" ht="30">
+    <row r="4" spans="1:20" s="5" customFormat="1">
       <c r="A4" s="35" t="s">
         <v>13</v>
       </c>
@@ -1516,12 +1510,8 @@
       </c>
       <c r="D4" s="39"/>
       <c r="E4" s="35"/>
-      <c r="F4" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="G4" s="39" t="s">
-        <v>182</v>
-      </c>
+      <c r="F4" s="40"/>
+      <c r="G4" s="39"/>
       <c r="H4" s="35"/>
       <c r="I4" s="35"/>
       <c r="J4" s="35" t="s">
@@ -1679,7 +1669,7 @@
         <v>55</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>60</v>
@@ -1764,13 +1754,13 @@
     </row>
     <row r="12" spans="1:20" s="8" customFormat="1">
       <c r="A12" s="31" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
@@ -1797,17 +1787,17 @@
         <v>14</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D13" s="34"/>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
       <c r="G13" s="34"/>
       <c r="H13" s="31" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I13" s="32"/>
       <c r="J13" s="34" t="s">
@@ -1829,21 +1819,21 @@
         <v>14</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D14" s="34"/>
       <c r="E14" s="34"/>
       <c r="F14" s="34" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H14" s="31" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I14" s="32"/>
       <c r="J14" s="34" t="s">
@@ -1862,22 +1852,22 @@
     </row>
     <row r="15" spans="1:20" s="8" customFormat="1">
       <c r="A15" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D15" s="34"/>
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
       <c r="G15" s="34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I15" s="32"/>
       <c r="J15" s="34" t="s">
@@ -1916,7 +1906,7 @@
       </c>
       <c r="H16" s="35"/>
       <c r="I16" s="35" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J16" s="35" t="s">
         <v>12</v>
@@ -3046,7 +3036,7 @@
         <v>170</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D54" s="11"/>
       <c r="E54" s="28"/>
@@ -3078,7 +3068,7 @@
         <v>171</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D55" s="11"/>
       <c r="E55" s="28"/>
@@ -3107,10 +3097,10 @@
         <v>15</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>47</v>
@@ -3122,7 +3112,7 @@
         <v>169</v>
       </c>
       <c r="I56" s="28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J56" s="15" t="s">
         <v>12</v>
@@ -3202,7 +3192,7 @@
         <v>174</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="16"/>
@@ -3234,7 +3224,7 @@
         <v>175</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="16"/>
@@ -3263,10 +3253,10 @@
         <v>15</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>47</v>
@@ -3278,7 +3268,7 @@
         <v>173</v>
       </c>
       <c r="I61" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J61" s="15" t="s">
         <v>12</v>
@@ -3629,26 +3619,26 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="64" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>210</v>
-      </c>
-      <c r="B20" s="64" t="s">
-        <v>211</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>212</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="22"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="64" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D21" s="64"/>
       <c r="E21" s="22"/>
@@ -3681,10 +3671,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>

--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1382D9C5-DE0B-4446-B9DA-5814B2B3E290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA9B861-64A9-4D98-BAAC-E71AA94DACCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="203">
   <si>
     <t>type</t>
   </si>
@@ -597,12 +597,6 @@
     <t>(${q_autre_quantite_2a} + ${q_autre_quantite_2b})*12</t>
   </si>
   <si>
-    <t>sn_sppa_impact_2510_4_qualite</t>
-  </si>
-  <si>
-    <t>(2025 Oct) - 4. SCH/STH – Contrôle Qualité</t>
-  </si>
-  <si>
     <t>q_sppa2510</t>
   </si>
   <si>
@@ -612,42 +606,9 @@
     <t>Méthode de capture code QR / code-barres</t>
   </si>
   <si>
-    <t>Veuillez saisir le code QR/code-barres</t>
-  </si>
-  <si>
-    <t>Veuillez répété le code QR/code-barres</t>
-  </si>
-  <si>
-    <t>Veuillez ressaisir le code QR / code-barres</t>
-  </si>
-  <si>
-    <t>barcode</t>
-  </si>
-  <si>
-    <t>Veuillez scanner le code-barres</t>
-  </si>
-  <si>
     <t>q_barcode_method</t>
   </si>
   <si>
-    <t>${q_barcode_method} = 'QRManual'</t>
-  </si>
-  <si>
-    <t>${q_barcode_method} = 'QRScann'</t>
-  </si>
-  <si>
-    <t>q_code_id1</t>
-  </si>
-  <si>
-    <t>q_code_id2</t>
-  </si>
-  <si>
-    <t>. = ${q_code_id1}</t>
-  </si>
-  <si>
-    <t>q_code_id3</t>
-  </si>
-  <si>
     <t>barcode_method</t>
   </si>
   <si>
@@ -663,7 +624,13 @@
     <t>Saisie manuelle (en cas de panne du scanner)</t>
   </si>
   <si>
-    <t>if(${q_barcode_method} = 'QRManual', concat(${q_code_id1}), concat(${q_code_id3}))</t>
+    <t>col_6</t>
+  </si>
+  <si>
+    <t>(2025 Oct) - 4. SCH/STH – Contrôle Qualité V2</t>
+  </si>
+  <si>
+    <t>sn_sppa_impact_2510_4_qualite_v2</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="19.625" style="7" customWidth="1"/>
@@ -1669,7 +1636,7 @@
         <v>55</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>60</v>
@@ -1754,13 +1721,13 @@
     </row>
     <row r="12" spans="1:20" s="8" customFormat="1">
       <c r="A12" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>201</v>
-      </c>
       <c r="C12" s="32" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
@@ -1782,170 +1749,148 @@
       <c r="S12" s="28"/>
       <c r="T12" s="28"/>
     </row>
-    <row r="13" spans="1:20" s="8" customFormat="1">
-      <c r="A13" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="28"/>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
-    </row>
-    <row r="14" spans="1:20" s="8" customFormat="1">
-      <c r="A14" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34" t="s">
-        <v>206</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="28"/>
-      <c r="Q14" s="28"/>
-      <c r="R14" s="28"/>
-      <c r="S14" s="28"/>
-      <c r="T14" s="28"/>
-    </row>
-    <row r="15" spans="1:20" s="8" customFormat="1">
-      <c r="A15" s="34" t="s">
-        <v>199</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="C15" s="34" t="s">
+    <row r="13" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A13" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="35"/>
+      <c r="O13" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-    </row>
-    <row r="16" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A16" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="J16" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="35" t="s">
-        <v>12</v>
-      </c>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" s="5" customFormat="1">
+      <c r="A14" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="39"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="13"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+    </row>
+    <row r="15" spans="1:20" s="30" customFormat="1">
+      <c r="A15" s="52"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="52"/>
+      <c r="K15" s="52"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="52"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="52"/>
+      <c r="R15" s="52"/>
+      <c r="S15" s="52"/>
+      <c r="T15" s="52"/>
+    </row>
+    <row r="16" spans="1:20" s="5" customFormat="1">
+      <c r="A16" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="54"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="35"/>
       <c r="N16" s="35"/>
-      <c r="O16" s="28"/>
+      <c r="O16" s="35"/>
       <c r="P16" s="35"/>
       <c r="Q16" s="35"/>
       <c r="R16" s="35"/>
       <c r="S16" s="35"/>
-      <c r="T16" s="35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" s="5" customFormat="1">
-      <c r="A17" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="39"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K17" s="13"/>
+      <c r="T16" s="35"/>
+    </row>
+    <row r="17" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A17" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17" s="35"/>
       <c r="L17" s="42"/>
       <c r="M17" s="35"/>
       <c r="N17" s="35"/>
@@ -1956,47 +1901,49 @@
       <c r="S17" s="35"/>
       <c r="T17" s="35"/>
     </row>
-    <row r="18" spans="1:20" s="30" customFormat="1">
-      <c r="A18" s="52"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
-      <c r="G18" s="52"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="52"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="52"/>
-      <c r="O18" s="52"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="52"/>
-      <c r="R18" s="52"/>
-      <c r="S18" s="52"/>
-      <c r="T18" s="52"/>
+    <row r="18" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A18" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="35"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
     </row>
     <row r="19" spans="1:20" s="5" customFormat="1">
-      <c r="A19" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="54"/>
-      <c r="L19" s="55"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="42"/>
       <c r="M19" s="35"/>
       <c r="N19" s="35"/>
       <c r="O19" s="35"/>
@@ -2011,23 +1958,29 @@
         <v>15</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="12"/>
+        <v>92</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="E20" s="16"/>
       <c r="F20" s="13"/>
       <c r="G20" s="17"/>
       <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
+      <c r="I20" s="16" t="s">
+        <v>131</v>
+      </c>
       <c r="J20" s="13" t="s">
         <v>12</v>
       </c>
       <c r="K20" s="35"/>
       <c r="L20" s="42"/>
-      <c r="M20" s="35"/>
+      <c r="M20" s="35" t="s">
+        <v>12</v>
+      </c>
       <c r="N20" s="35"/>
       <c r="O20" s="35"/>
       <c r="P20" s="35"/>
@@ -2036,25 +1989,17 @@
       <c r="S20" s="35"/>
       <c r="T20" s="35"/>
     </row>
-    <row r="21" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>91</v>
-      </c>
+    <row r="21" spans="1:20" s="5" customFormat="1">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="11"/>
       <c r="D21" s="12"/>
       <c r="E21" s="16"/>
       <c r="F21" s="13"/>
       <c r="G21" s="17"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
-      <c r="J21" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="J21" s="13"/>
       <c r="K21" s="35"/>
       <c r="L21" s="42"/>
       <c r="M21" s="35"/>
@@ -2067,19 +2012,27 @@
       <c r="T21" s="35"/>
     </row>
     <row r="22" spans="1:20" s="5" customFormat="1">
-      <c r="A22" s="13"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="35"/>
+      <c r="A22" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="56"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="54"/>
       <c r="N22" s="35"/>
       <c r="O22" s="35"/>
       <c r="P22" s="35"/>
@@ -2088,34 +2041,28 @@
       <c r="S22" s="35"/>
       <c r="T22" s="35"/>
     </row>
-    <row r="23" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A23" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K23" s="35"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="35" t="s">
-        <v>12</v>
-      </c>
+    <row r="23" spans="1:20" s="5" customFormat="1">
+      <c r="A23" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" s="56"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="56"/>
+      <c r="H23" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="54"/>
       <c r="N23" s="35"/>
       <c r="O23" s="35"/>
       <c r="P23" s="35"/>
@@ -2125,19 +2072,19 @@
       <c r="T23" s="35"/>
     </row>
     <row r="24" spans="1:20" s="5" customFormat="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="35"/>
+      <c r="A24" s="54"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="54"/>
       <c r="N24" s="35"/>
       <c r="O24" s="35"/>
       <c r="P24" s="35"/>
@@ -2147,27 +2094,29 @@
       <c r="T24" s="35"/>
     </row>
     <row r="25" spans="1:20" s="5" customFormat="1">
-      <c r="A25" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="54"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="56"/>
+      <c r="A25" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="17"/>
       <c r="H25" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="I25" s="54"/>
-      <c r="J25" s="54"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="54"/>
+        <v>134</v>
+      </c>
+      <c r="I25" s="28"/>
+      <c r="J25" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="35"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="35"/>
       <c r="N25" s="35"/>
       <c r="O25" s="35"/>
       <c r="P25" s="35"/>
@@ -2177,27 +2126,29 @@
       <c r="T25" s="35"/>
     </row>
     <row r="26" spans="1:20" s="5" customFormat="1">
-      <c r="A26" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="54"/>
-      <c r="F26" s="54"/>
-      <c r="G26" s="56"/>
+      <c r="A26" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="17"/>
       <c r="H26" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="I26" s="54"/>
-      <c r="J26" s="54"/>
-      <c r="K26" s="54"/>
-      <c r="L26" s="55"/>
-      <c r="M26" s="54"/>
+        <v>134</v>
+      </c>
+      <c r="I26" s="28"/>
+      <c r="J26" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" s="35"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="35"/>
       <c r="N26" s="35"/>
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
@@ -2206,20 +2157,36 @@
       <c r="S26" s="35"/>
       <c r="T26" s="35"/>
     </row>
-    <row r="27" spans="1:20" s="5" customFormat="1">
-      <c r="A27" s="54"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="54"/>
+    <row r="27" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A27" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="39"/>
+      <c r="H27" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K27" s="35"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="35" t="s">
+        <v>12</v>
+      </c>
       <c r="N27" s="35"/>
       <c r="O27" s="35"/>
       <c r="P27" s="35"/>
@@ -2228,100 +2195,80 @@
       <c r="S27" s="35"/>
       <c r="T27" s="35"/>
     </row>
-    <row r="28" spans="1:20" s="5" customFormat="1">
-      <c r="A28" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I28" s="28"/>
-      <c r="J28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K28" s="35"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-    </row>
-    <row r="29" spans="1:20" s="5" customFormat="1">
-      <c r="A29" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I29" s="28"/>
-      <c r="J29" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="35"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-    </row>
-    <row r="30" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A30" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="39" t="s">
-        <v>47</v>
-      </c>
+    <row r="28" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A28" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="J28" s="15"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+    </row>
+    <row r="29" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A29" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="J29" s="15"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+    </row>
+    <row r="30" spans="1:20" s="5" customFormat="1">
+      <c r="A30" s="13"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
       <c r="E30" s="35"/>
       <c r="F30" s="35"/>
       <c r="G30" s="39"/>
-      <c r="H30" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="I30" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
       <c r="K30" s="35"/>
       <c r="L30" s="42"/>
-      <c r="M30" s="35" t="s">
-        <v>12</v>
-      </c>
+      <c r="M30" s="35"/>
       <c r="N30" s="35"/>
       <c r="O30" s="35"/>
       <c r="P30" s="35"/>
@@ -2330,80 +2277,100 @@
       <c r="S30" s="35"/>
       <c r="T30" s="35"/>
     </row>
-    <row r="31" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A31" s="15" t="s">
-        <v>53</v>
+    <row r="31" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A31" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I31" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="J31" s="15"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28"/>
-      <c r="P31" s="28"/>
-      <c r="Q31" s="28"/>
-      <c r="R31" s="28"/>
-      <c r="S31" s="28"/>
-      <c r="T31" s="28"/>
-    </row>
-    <row r="32" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A32" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I32" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-    </row>
-    <row r="33" spans="1:20" s="5" customFormat="1">
-      <c r="A33" s="13"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
+        <v>143</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I31" s="28"/>
+      <c r="J31" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" s="35"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+    </row>
+    <row r="32" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A32" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I32" s="28"/>
+      <c r="J32" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" s="35"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+    </row>
+    <row r="33" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A33" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I33" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="K33" s="35"/>
       <c r="L33" s="42"/>
-      <c r="M33" s="35"/>
+      <c r="M33" s="35" t="s">
+        <v>12</v>
+      </c>
       <c r="N33" s="35"/>
       <c r="O33" s="35"/>
       <c r="P33" s="35"/>
@@ -2412,100 +2379,80 @@
       <c r="S33" s="35"/>
       <c r="T33" s="35"/>
     </row>
-    <row r="34" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A34" s="13" t="s">
-        <v>15</v>
+    <row r="34" spans="1:20" s="8" customFormat="1" ht="47.25">
+      <c r="A34" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I34" s="28"/>
-      <c r="J34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K34" s="35"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-    </row>
-    <row r="35" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A35" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="28"/>
-      <c r="J35" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K35" s="35"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35"/>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-    </row>
-    <row r="36" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A36" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>47</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="J34" s="15"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="28"/>
+      <c r="S34" s="28"/>
+      <c r="T34" s="28"/>
+    </row>
+    <row r="35" spans="1:20" s="8" customFormat="1" ht="47.25">
+      <c r="A35" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="J35" s="15"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+    </row>
+    <row r="36" spans="1:20" s="5" customFormat="1">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="12"/>
       <c r="E36" s="16"/>
       <c r="F36" s="13"/>
       <c r="G36" s="17"/>
-      <c r="H36" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I36" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="13"/>
       <c r="K36" s="35"/>
       <c r="L36" s="42"/>
-      <c r="M36" s="35" t="s">
-        <v>12</v>
-      </c>
+      <c r="M36" s="35"/>
       <c r="N36" s="35"/>
       <c r="O36" s="35"/>
       <c r="P36" s="35"/>
@@ -2514,80 +2461,100 @@
       <c r="S36" s="35"/>
       <c r="T36" s="35"/>
     </row>
-    <row r="37" spans="1:20" s="8" customFormat="1" ht="47.25">
-      <c r="A37" s="15" t="s">
-        <v>53</v>
+    <row r="37" spans="1:20" s="5" customFormat="1">
+      <c r="A37" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I37" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="J37" s="15"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-    </row>
-    <row r="38" spans="1:20" s="8" customFormat="1" ht="47.25">
-      <c r="A38" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="J38" s="15"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="28"/>
-      <c r="P38" s="28"/>
-      <c r="Q38" s="28"/>
-      <c r="R38" s="28"/>
-      <c r="S38" s="28"/>
-      <c r="T38" s="28"/>
-    </row>
-    <row r="39" spans="1:20" s="5" customFormat="1">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="12"/>
+        <v>151</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" s="35"/>
+      <c r="J37" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K37" s="35"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="35"/>
+    </row>
+    <row r="38" spans="1:20" s="5" customFormat="1">
+      <c r="A38" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="28"/>
+      <c r="J38" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" s="35"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="35"/>
+    </row>
+    <row r="39" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A39" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="E39" s="16"/>
       <c r="F39" s="13"/>
       <c r="G39" s="17"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="13"/>
+      <c r="H39" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I39" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="K39" s="35"/>
       <c r="L39" s="42"/>
-      <c r="M39" s="35"/>
+      <c r="M39" s="35" t="s">
+        <v>12</v>
+      </c>
       <c r="N39" s="35"/>
       <c r="O39" s="35"/>
       <c r="P39" s="35"/>
@@ -2596,100 +2563,80 @@
       <c r="S39" s="35"/>
       <c r="T39" s="35"/>
     </row>
-    <row r="40" spans="1:20" s="5" customFormat="1">
-      <c r="A40" s="13" t="s">
-        <v>15</v>
+    <row r="40" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A40" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="12"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I40" s="35"/>
-      <c r="J40" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40" s="35"/>
-      <c r="L40" s="42"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="35"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="35"/>
-      <c r="S40" s="35"/>
-      <c r="T40" s="35"/>
-    </row>
-    <row r="41" spans="1:20" s="5" customFormat="1">
-      <c r="A41" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" s="28"/>
-      <c r="J41" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K41" s="35"/>
-      <c r="L41" s="42"/>
-      <c r="M41" s="35"/>
-      <c r="N41" s="35"/>
-      <c r="O41" s="35"/>
-      <c r="P41" s="35"/>
-      <c r="Q41" s="35"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="35"/>
-    </row>
-    <row r="42" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A42" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>47</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I40" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="J40" s="15"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+    </row>
+    <row r="41" spans="1:20" s="8" customFormat="1" ht="47.25">
+      <c r="A41" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="28"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I41" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="J41" s="15"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="28"/>
+      <c r="P41" s="28"/>
+      <c r="Q41" s="28"/>
+      <c r="R41" s="28"/>
+      <c r="S41" s="28"/>
+      <c r="T41" s="28"/>
+    </row>
+    <row r="42" spans="1:20" s="5" customFormat="1">
+      <c r="A42" s="13"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
       <c r="E42" s="16"/>
       <c r="F42" s="13"/>
       <c r="G42" s="17"/>
-      <c r="H42" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I42" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="13"/>
       <c r="K42" s="35"/>
       <c r="L42" s="42"/>
-      <c r="M42" s="35" t="s">
-        <v>12</v>
-      </c>
+      <c r="M42" s="35"/>
       <c r="N42" s="35"/>
       <c r="O42" s="35"/>
       <c r="P42" s="35"/>
@@ -2698,80 +2645,100 @@
       <c r="S42" s="35"/>
       <c r="T42" s="35"/>
     </row>
-    <row r="43" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A43" s="15" t="s">
-        <v>53</v>
+    <row r="43" spans="1:20" s="5" customFormat="1">
+      <c r="A43" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I43" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="J43" s="15"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-    </row>
-    <row r="44" spans="1:20" s="8" customFormat="1" ht="47.25">
-      <c r="A44" s="15" t="s">
-        <v>53</v>
+        <v>159</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D43" s="12"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I43" s="28"/>
+      <c r="J43" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K43" s="35"/>
+      <c r="L43" s="42"/>
+      <c r="M43" s="35"/>
+      <c r="N43" s="35"/>
+      <c r="O43" s="35"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
+    </row>
+    <row r="44" spans="1:20" s="5" customFormat="1">
+      <c r="A44" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I44" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J44" s="15"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28"/>
-      <c r="P44" s="28"/>
-      <c r="Q44" s="28"/>
-      <c r="R44" s="28"/>
-      <c r="S44" s="28"/>
-      <c r="T44" s="28"/>
-    </row>
-    <row r="45" spans="1:20" s="5" customFormat="1">
-      <c r="A45" s="13"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
+        <v>160</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D44" s="12"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I44" s="28"/>
+      <c r="J44" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K44" s="35"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
+    </row>
+    <row r="45" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A45" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="E45" s="16"/>
       <c r="F45" s="13"/>
       <c r="G45" s="17"/>
-      <c r="H45" s="16"/>
-      <c r="I45" s="16"/>
-      <c r="J45" s="13"/>
+      <c r="H45" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I45" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>12</v>
+      </c>
       <c r="K45" s="35"/>
       <c r="L45" s="42"/>
-      <c r="M45" s="35"/>
+      <c r="M45" s="35" t="s">
+        <v>12</v>
+      </c>
       <c r="N45" s="35"/>
       <c r="O45" s="35"/>
       <c r="P45" s="35"/>
@@ -2780,127 +2747,109 @@
       <c r="S45" s="35"/>
       <c r="T45" s="35"/>
     </row>
-    <row r="46" spans="1:20" s="5" customFormat="1">
-      <c r="A46" s="13" t="s">
-        <v>15</v>
+    <row r="46" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A46" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="12"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="28"/>
-      <c r="J46" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K46" s="35"/>
-      <c r="L46" s="42"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="35"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-    </row>
-    <row r="47" spans="1:20" s="5" customFormat="1">
-      <c r="A47" s="13" t="s">
-        <v>15</v>
+        <v>163</v>
+      </c>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J46" s="15"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+    </row>
+    <row r="47" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A47" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" s="12"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I47" s="28"/>
-      <c r="J47" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K47" s="35"/>
-      <c r="L47" s="42"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35"/>
-    </row>
-    <row r="48" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A48" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="16"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I48" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K48" s="35"/>
-      <c r="L48" s="42"/>
-      <c r="M48" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N48" s="35"/>
-      <c r="O48" s="35"/>
-      <c r="P48" s="35"/>
-      <c r="Q48" s="35"/>
-      <c r="R48" s="35"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
+        <v>165</v>
+      </c>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="I47" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="J47" s="15"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
+      <c r="T47" s="28"/>
+    </row>
+    <row r="48" spans="1:20" s="8" customFormat="1">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="S48" s="28"/>
+      <c r="T48" s="28"/>
     </row>
     <row r="49" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A49" s="15" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" s="11"/>
+        <v>167</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>70</v>
+      </c>
       <c r="D49" s="11"/>
       <c r="E49" s="28"/>
       <c r="F49" s="15"/>
       <c r="G49" s="57"/>
-      <c r="H49" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I49" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="J49" s="15"/>
+      <c r="H49" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I49" s="28"/>
+      <c r="J49" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="K49" s="28"/>
       <c r="L49" s="28"/>
       <c r="M49" s="28"/>
@@ -2912,25 +2861,27 @@
       <c r="S49" s="28"/>
       <c r="T49" s="28"/>
     </row>
-    <row r="50" spans="1:20" s="8" customFormat="1" ht="31.5">
+    <row r="50" spans="1:20" s="8" customFormat="1">
       <c r="A50" s="15" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="C50" s="11"/>
+        <v>168</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>74</v>
+      </c>
       <c r="D50" s="11"/>
       <c r="E50" s="28"/>
       <c r="F50" s="15"/>
       <c r="G50" s="57"/>
       <c r="H50" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I50" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="J50" s="15"/>
+        <v>169</v>
+      </c>
+      <c r="I50" s="28"/>
+      <c r="J50" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="K50" s="28"/>
       <c r="L50" s="28"/>
       <c r="M50" s="28"/>
@@ -2942,17 +2893,27 @@
       <c r="S50" s="28"/>
       <c r="T50" s="28"/>
     </row>
-    <row r="51" spans="1:20" s="8" customFormat="1">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="11"/>
+    <row r="51" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A51" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>181</v>
+      </c>
       <c r="D51" s="11"/>
       <c r="E51" s="28"/>
       <c r="F51" s="15"/>
       <c r="G51" s="57"/>
-      <c r="H51" s="58"/>
+      <c r="H51" s="58" t="s">
+        <v>169</v>
+      </c>
       <c r="I51" s="28"/>
-      <c r="J51" s="15"/>
+      <c r="J51" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="K51" s="28"/>
       <c r="L51" s="28"/>
       <c r="M51" s="28"/>
@@ -2966,20 +2927,20 @@
     </row>
     <row r="52" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A52" s="15" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="D52" s="11"/>
       <c r="E52" s="28"/>
       <c r="F52" s="15"/>
       <c r="G52" s="57"/>
-      <c r="H52" s="28" t="s">
-        <v>134</v>
+      <c r="H52" s="58" t="s">
+        <v>169</v>
       </c>
       <c r="I52" s="28"/>
       <c r="J52" s="15" t="s">
@@ -2996,30 +2957,36 @@
       <c r="S52" s="28"/>
       <c r="T52" s="28"/>
     </row>
-    <row r="53" spans="1:20" s="8" customFormat="1">
+    <row r="53" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A53" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D53" s="11"/>
+        <v>184</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="E53" s="28"/>
       <c r="F53" s="15"/>
       <c r="G53" s="57"/>
       <c r="H53" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="I53" s="28"/>
+      <c r="I53" s="28" t="s">
+        <v>185</v>
+      </c>
       <c r="J53" s="15" t="s">
         <v>12</v>
       </c>
       <c r="K53" s="28"/>
       <c r="L53" s="28"/>
-      <c r="M53" s="28"/>
+      <c r="M53" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="N53" s="28"/>
       <c r="O53" s="28"/>
       <c r="P53" s="28"/>
@@ -3028,119 +2995,113 @@
       <c r="S53" s="28"/>
       <c r="T53" s="28"/>
     </row>
-    <row r="54" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A54" s="15" t="s">
+    <row r="54" spans="1:20" s="5" customFormat="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="15"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+    </row>
+    <row r="55" spans="1:20" s="5" customFormat="1">
+      <c r="A55" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="I55" s="16"/>
+      <c r="J55" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K55" s="35"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="35"/>
+      <c r="N55" s="35"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+      <c r="R55" s="35"/>
+      <c r="S55" s="35"/>
+      <c r="T55" s="35"/>
+    </row>
+    <row r="56" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A56" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B54" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="D54" s="11"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="I54" s="28"/>
-      <c r="J54" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="28"/>
-      <c r="R54" s="28"/>
-      <c r="S54" s="28"/>
-      <c r="T54" s="28"/>
-    </row>
-    <row r="55" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A55" s="15" t="s">
+      <c r="B56" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D56" s="12"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="I56" s="16"/>
+      <c r="J56" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K56" s="35"/>
+      <c r="L56" s="42"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
+    </row>
+    <row r="57" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A57" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B55" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D55" s="11"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="I55" s="28"/>
-      <c r="J55" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-    </row>
-    <row r="56" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A56" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E56" s="28"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="I56" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="J56" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K56" s="28"/>
-      <c r="L56" s="28"/>
-      <c r="M56" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="N56" s="28"/>
-      <c r="O56" s="28"/>
-      <c r="P56" s="28"/>
-      <c r="Q56" s="28"/>
-      <c r="R56" s="28"/>
-      <c r="S56" s="28"/>
-      <c r="T56" s="28"/>
-    </row>
-    <row r="57" spans="1:20" s="5" customFormat="1">
-      <c r="A57" s="13"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="11"/>
+      <c r="B57" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>187</v>
+      </c>
       <c r="D57" s="12"/>
       <c r="E57" s="16"/>
       <c r="F57" s="13"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="16"/>
+      <c r="H57" s="58" t="s">
+        <v>173</v>
+      </c>
       <c r="I57" s="16"/>
-      <c r="J57" s="13"/>
+      <c r="J57" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="K57" s="35"/>
       <c r="L57" s="42"/>
       <c r="M57" s="35"/>
@@ -3152,30 +3113,36 @@
       <c r="S57" s="35"/>
       <c r="T57" s="35"/>
     </row>
-    <row r="58" spans="1:20" s="5" customFormat="1">
+    <row r="58" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A58" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" s="12"/>
+        <v>189</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="E58" s="16"/>
       <c r="F58" s="13"/>
       <c r="G58" s="17"/>
       <c r="H58" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="I58" s="16"/>
+      <c r="I58" s="28" t="s">
+        <v>190</v>
+      </c>
       <c r="J58" s="15" t="s">
         <v>12</v>
       </c>
       <c r="K58" s="35"/>
       <c r="L58" s="42"/>
-      <c r="M58" s="35"/>
+      <c r="M58" s="35" t="s">
+        <v>12</v>
+      </c>
       <c r="N58" s="35"/>
       <c r="O58" s="35"/>
       <c r="P58" s="35"/>
@@ -3184,27 +3151,17 @@
       <c r="S58" s="35"/>
       <c r="T58" s="35"/>
     </row>
-    <row r="59" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A59" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>186</v>
-      </c>
+    <row r="59" spans="1:20" s="5" customFormat="1">
+      <c r="A59" s="13"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="11"/>
       <c r="D59" s="12"/>
       <c r="E59" s="16"/>
       <c r="F59" s="13"/>
       <c r="G59" s="17"/>
-      <c r="H59" s="58" t="s">
-        <v>173</v>
-      </c>
+      <c r="H59" s="16"/>
       <c r="I59" s="16"/>
-      <c r="J59" s="15" t="s">
-        <v>12</v>
-      </c>
+      <c r="J59" s="13"/>
       <c r="K59" s="35"/>
       <c r="L59" s="42"/>
       <c r="M59" s="35"/>
@@ -3216,108 +3173,92 @@
       <c r="S59" s="35"/>
       <c r="T59" s="35"/>
     </row>
-    <row r="60" spans="1:20" s="5" customFormat="1" ht="31.5">
+    <row r="60" spans="1:20">
       <c r="A60" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D60" s="12"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="I60" s="16"/>
-      <c r="J60" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K60" s="35"/>
-      <c r="L60" s="42"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="35"/>
-      <c r="O60" s="35"/>
-      <c r="P60" s="35"/>
-      <c r="Q60" s="35"/>
-      <c r="R60" s="35"/>
-      <c r="S60" s="35"/>
-      <c r="T60" s="35"/>
-    </row>
-    <row r="61" spans="1:20" s="5" customFormat="1" ht="31.5">
+        <v>14</v>
+      </c>
+      <c r="B60" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C60" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="D60" s="61"/>
+      <c r="E60" s="62"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="61"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="62"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="62"/>
+      <c r="L60" s="62"/>
+      <c r="M60" s="62"/>
+      <c r="N60" s="62"/>
+      <c r="O60" s="62"/>
+      <c r="P60" s="62"/>
+      <c r="Q60" s="62"/>
+      <c r="R60" s="62"/>
+      <c r="S60" s="62"/>
+      <c r="T60" s="62"/>
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="I61" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="J61" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K61" s="35"/>
-      <c r="L61" s="42"/>
-      <c r="M61" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N61" s="35"/>
-      <c r="O61" s="35"/>
-      <c r="P61" s="35"/>
-      <c r="Q61" s="35"/>
-      <c r="R61" s="35"/>
-      <c r="S61" s="35"/>
-      <c r="T61" s="35"/>
-    </row>
-    <row r="62" spans="1:20" s="5" customFormat="1">
-      <c r="A62" s="13"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="17"/>
+        <v>59</v>
+      </c>
+      <c r="B61" s="59"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="61"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="62"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="62"/>
+      <c r="L61" s="62"/>
+      <c r="M61" s="62"/>
+      <c r="N61" s="62"/>
+      <c r="O61" s="62"/>
+      <c r="P61" s="62"/>
+      <c r="Q61" s="62"/>
+      <c r="R61" s="62"/>
+      <c r="S61" s="62"/>
+      <c r="T61" s="62"/>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B62" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="63"/>
+      <c r="D62" s="61"/>
+      <c r="E62" s="62"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="61"/>
       <c r="H62" s="16"/>
-      <c r="I62" s="16"/>
+      <c r="I62" s="62"/>
       <c r="J62" s="13"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="42"/>
-      <c r="M62" s="35"/>
-      <c r="N62" s="35"/>
-      <c r="O62" s="35"/>
-      <c r="P62" s="35"/>
-      <c r="Q62" s="35"/>
-      <c r="R62" s="35"/>
-      <c r="S62" s="35"/>
-      <c r="T62" s="35"/>
+      <c r="K62" s="62"/>
+      <c r="L62" s="62"/>
+      <c r="M62" s="62"/>
+      <c r="N62" s="62"/>
+      <c r="O62" s="62"/>
+      <c r="P62" s="62"/>
+      <c r="Q62" s="62"/>
+      <c r="R62" s="62"/>
+      <c r="S62" s="62"/>
+      <c r="T62" s="62"/>
     </row>
     <row r="63" spans="1:20">
-      <c r="A63" s="13" t="s">
-        <v>14</v>
+      <c r="A63" s="59" t="s">
+        <v>17</v>
       </c>
       <c r="B63" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="C63" s="60" t="s">
-        <v>105</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="C63" s="63"/>
       <c r="D63" s="61"/>
       <c r="E63" s="62"/>
       <c r="F63" s="59"/>
@@ -3335,82 +3276,6 @@
       <c r="R63" s="62"/>
       <c r="S63" s="62"/>
       <c r="T63" s="62"/>
-    </row>
-    <row r="64" spans="1:20">
-      <c r="A64" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64" s="59"/>
-      <c r="C64" s="63"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="62"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="62"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="62"/>
-      <c r="L64" s="62"/>
-      <c r="M64" s="62"/>
-      <c r="N64" s="62"/>
-      <c r="O64" s="62"/>
-      <c r="P64" s="62"/>
-      <c r="Q64" s="62"/>
-      <c r="R64" s="62"/>
-      <c r="S64" s="62"/>
-      <c r="T64" s="62"/>
-    </row>
-    <row r="65" spans="1:20">
-      <c r="A65" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B65" s="59" t="s">
-        <v>177</v>
-      </c>
-      <c r="C65" s="63"/>
-      <c r="D65" s="61"/>
-      <c r="E65" s="62"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="62"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="62"/>
-      <c r="L65" s="62"/>
-      <c r="M65" s="62"/>
-      <c r="N65" s="62"/>
-      <c r="O65" s="62"/>
-      <c r="P65" s="62"/>
-      <c r="Q65" s="62"/>
-      <c r="R65" s="62"/>
-      <c r="S65" s="62"/>
-      <c r="T65" s="62"/>
-    </row>
-    <row r="66" spans="1:20">
-      <c r="A66" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="B66" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" s="63"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="62"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="16"/>
-      <c r="I66" s="62"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="62"/>
-      <c r="L66" s="62"/>
-      <c r="M66" s="62"/>
-      <c r="N66" s="62"/>
-      <c r="O66" s="62"/>
-      <c r="P66" s="62"/>
-      <c r="Q66" s="62"/>
-      <c r="R66" s="62"/>
-      <c r="S66" s="62"/>
-      <c r="T66" s="62"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3619,26 +3484,26 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="64" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="22"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="64" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="D21" s="64"/>
       <c r="E21" s="22"/>
@@ -3671,10 +3536,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>

--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA9B861-64A9-4D98-BAAC-E71AA94DACCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC8F408-1D85-451A-B8F8-1481EED22012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="200">
   <si>
     <t>type</t>
   </si>
@@ -598,15 +598,6 @@
   </si>
   <si>
     <t>q_sppa2510</t>
-  </si>
-  <si>
-    <t>select_one barcode_method</t>
-  </si>
-  <si>
-    <t>Méthode de capture code QR / code-barres</t>
-  </si>
-  <si>
-    <t>q_barcode_method</t>
   </si>
   <si>
     <t>barcode_method</t>
@@ -726,7 +717,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,12 +784,6 @@
         <bgColor rgb="FFFBE4D5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -858,7 +843,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -935,18 +920,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1317,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T63"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="19.625" style="7" customWidth="1"/>
@@ -1336,75 +1309,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="36" t="s">
+      <c r="J1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="36" t="s">
+      <c r="L1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="P1" s="37" t="s">
+      <c r="P1" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="33" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="6" customFormat="1" ht="31.5">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="35" t="s">
         <v>82</v>
       </c>
       <c r="D2" s="12" t="s">
@@ -1434,13 +1407,13 @@
       <c r="T2" s="16"/>
     </row>
     <row r="3" spans="1:20" s="6" customFormat="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="35" t="s">
         <v>83</v>
       </c>
       <c r="D3" s="12"/>
@@ -1466,140 +1439,140 @@
       <c r="T3" s="16"/>
     </row>
     <row r="4" spans="1:20" s="5" customFormat="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35" t="s">
+      <c r="D4" s="35"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31" t="s">
         <v>12</v>
       </c>
       <c r="K4" s="13"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
       <c r="O4" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
     </row>
     <row r="5" spans="1:20" s="5" customFormat="1">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35" t="s">
+      <c r="D5" s="35"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31" t="s">
         <v>12</v>
       </c>
       <c r="K5" s="13"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
       <c r="O5" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35" t="s">
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
     </row>
     <row r="6" spans="1:20" s="5" customFormat="1">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="31" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="39"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35" t="s">
+      <c r="D6" s="35"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31" t="s">
         <v>12</v>
       </c>
       <c r="K6" s="13"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
       <c r="O6" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35" t="s">
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="S6" s="35"/>
-      <c r="T6" s="35"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
     </row>
     <row r="7" spans="1:20" s="5" customFormat="1">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="31" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="D7" s="39"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35" t="s">
+      <c r="D7" s="35"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31" t="s">
         <v>12</v>
       </c>
       <c r="K7" s="13"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
       <c r="O7" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35" t="s">
+      <c r="P7" s="31"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="T7" s="35"/>
+      <c r="T7" s="31"/>
     </row>
     <row r="8" spans="1:20" s="8" customFormat="1">
       <c r="A8" s="28" t="s">
@@ -1608,11 +1581,11 @@
       <c r="B8" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="28"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="15"/>
       <c r="I8" s="28" t="s">
         <v>121</v>
@@ -1632,26 +1605,26 @@
       <c r="T8" s="28"/>
     </row>
     <row r="9" spans="1:20" s="8" customFormat="1">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="43"/>
+      <c r="N9" s="43"/>
       <c r="O9" s="28"/>
       <c r="P9" s="28"/>
       <c r="Q9" s="28"/>
@@ -1666,11 +1639,11 @@
       <c r="B10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="28"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="46"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="15"/>
       <c r="I10" s="28" t="s">
         <v>57</v>
@@ -1696,11 +1669,11 @@
       <c r="B11" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
       <c r="E11" s="28"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="46"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="15"/>
       <c r="I11" s="28" t="s">
         <v>122</v>
@@ -1719,167 +1692,165 @@
       <c r="S11" s="28"/>
       <c r="T11" s="28"/>
     </row>
-    <row r="12" spans="1:20" s="8" customFormat="1">
+    <row r="12" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A12" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+        <v>13</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="31"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
-      <c r="S12" s="28"/>
-      <c r="T12" s="28"/>
-    </row>
-    <row r="13" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A13" s="35" t="s">
-        <v>13</v>
+      <c r="O12" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" s="5" customFormat="1">
+      <c r="A13" s="31" t="s">
+        <v>63</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31" t="s">
         <v>12</v>
       </c>
       <c r="K13" s="13"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N13" s="35"/>
-      <c r="O13" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="P13" s="35"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" s="5" customFormat="1">
-      <c r="A14" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-    </row>
-    <row r="15" spans="1:20" s="30" customFormat="1">
-      <c r="A15" s="52"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="52"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="52"/>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="52"/>
-      <c r="R15" s="52"/>
-      <c r="S15" s="52"/>
-      <c r="T15" s="52"/>
-    </row>
-    <row r="16" spans="1:20" s="5" customFormat="1">
-      <c r="A16" s="25" t="s">
+      <c r="L13" s="38"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+    </row>
+    <row r="14" spans="1:20" s="30" customFormat="1">
+      <c r="A14" s="48"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+    </row>
+    <row r="15" spans="1:20" s="5" customFormat="1">
+      <c r="A15" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B15" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C15" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+    </row>
+    <row r="16" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A16" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16" s="31"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A17" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="16"/>
@@ -1890,218 +1861,220 @@
       <c r="J17" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="35"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-    </row>
-    <row r="18" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A18" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>91</v>
-      </c>
+      <c r="K17" s="31"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+    </row>
+    <row r="18" spans="1:20" s="5" customFormat="1">
+      <c r="A18" s="13"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="11"/>
       <c r="D18" s="12"/>
       <c r="E18" s="16"/>
       <c r="F18" s="13"/>
       <c r="G18" s="17"/>
       <c r="H18" s="16"/>
       <c r="I18" s="16"/>
-      <c r="J18" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="35"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-    </row>
-    <row r="19" spans="1:20" s="5" customFormat="1">
-      <c r="A19" s="13"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+    </row>
+    <row r="19" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>48</v>
+      </c>
       <c r="E19" s="16"/>
       <c r="F19" s="13"/>
       <c r="G19" s="17"/>
       <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-    </row>
-    <row r="20" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A20" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>48</v>
-      </c>
+      <c r="I19" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="31"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+    </row>
+    <row r="20" spans="1:20" s="5" customFormat="1">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
       <c r="E20" s="16"/>
       <c r="F20" s="13"/>
       <c r="G20" s="17"/>
       <c r="H20" s="16"/>
-      <c r="I20" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="35"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
     </row>
     <row r="21" spans="1:20" s="5" customFormat="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
+      <c r="A21" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="52"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
     </row>
     <row r="22" spans="1:20" s="5" customFormat="1">
-      <c r="A22" s="54" t="s">
-        <v>44</v>
+      <c r="A22" s="50" t="s">
+        <v>67</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="56" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="56"/>
+        <v>133</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="52"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="52"/>
       <c r="H22" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
     </row>
     <row r="23" spans="1:20" s="5" customFormat="1">
-      <c r="A23" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C23" s="56" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
+      <c r="A23" s="50"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="51"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
     </row>
     <row r="24" spans="1:20" s="5" customFormat="1">
-      <c r="A24" s="54"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
+      <c r="A24" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="28"/>
+      <c r="J24" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" s="31"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
     </row>
     <row r="25" spans="1:20" s="5" customFormat="1">
       <c r="A25" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="16"/>
@@ -2114,104 +2087,102 @@
       <c r="J25" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K25" s="35"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-    </row>
-    <row r="26" spans="1:20" s="5" customFormat="1">
+      <c r="K25" s="31"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+    </row>
+    <row r="26" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A26" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="I26" s="28"/>
+      <c r="I26" s="31" t="s">
+        <v>137</v>
+      </c>
       <c r="J26" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K26" s="35"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-    </row>
-    <row r="27" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A27" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="I27" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K27" s="35"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N27" s="35"/>
-      <c r="O27" s="35"/>
-      <c r="P27" s="35"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+    </row>
+    <row r="27" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A27" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="J27" s="15"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
     </row>
     <row r="28" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A28" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="28"/>
       <c r="F28" s="15"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="58" t="s">
+      <c r="G28" s="53"/>
+      <c r="H28" s="54" t="s">
         <v>126</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="28"/>
@@ -2225,67 +2196,69 @@
       <c r="S28" s="28"/>
       <c r="T28" s="28"/>
     </row>
-    <row r="29" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A29" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-    </row>
-    <row r="30" spans="1:20" s="5" customFormat="1">
-      <c r="A30" s="13"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
+    <row r="29" spans="1:20" s="5" customFormat="1">
+      <c r="A29" s="13"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+    </row>
+    <row r="30" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A30" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I30" s="28"/>
+      <c r="J30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" s="31"/>
+      <c r="L30" s="38"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="31"/>
     </row>
     <row r="31" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A31" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>143</v>
+      <c r="B31" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="16"/>
@@ -2298,104 +2271,102 @@
       <c r="J31" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K31" s="35"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
     </row>
     <row r="32" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A32" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>144</v>
+      <c r="B32" s="15" t="s">
+        <v>145</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D32" s="12"/>
+        <v>98</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="E32" s="16"/>
       <c r="F32" s="13"/>
       <c r="G32" s="17"/>
       <c r="H32" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="I32" s="28"/>
+      <c r="I32" s="31" t="s">
+        <v>146</v>
+      </c>
       <c r="J32" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K32" s="35"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35"/>
-    </row>
-    <row r="33" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A33" s="13" t="s">
-        <v>15</v>
+      <c r="K32" s="31"/>
+      <c r="L32" s="38"/>
+      <c r="M32" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+    </row>
+    <row r="33" spans="1:20" s="8" customFormat="1" ht="47.25">
+      <c r="A33" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35"/>
+        <v>147</v>
+      </c>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="I33" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="J33" s="15"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="28"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
     </row>
     <row r="34" spans="1:20" s="8" customFormat="1" ht="47.25">
       <c r="A34" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
       <c r="E34" s="28"/>
       <c r="F34" s="15"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="58" t="s">
+      <c r="G34" s="53"/>
+      <c r="H34" s="54" t="s">
         <v>126</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J34" s="15"/>
       <c r="K34" s="28"/>
@@ -2409,67 +2380,69 @@
       <c r="S34" s="28"/>
       <c r="T34" s="28"/>
     </row>
-    <row r="35" spans="1:20" s="8" customFormat="1" ht="47.25">
-      <c r="A35" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>149</v>
-      </c>
+    <row r="35" spans="1:20" s="5" customFormat="1">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
       <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I35" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="J35" s="15"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="28"/>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
     </row>
     <row r="36" spans="1:20" s="5" customFormat="1">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="11"/>
+      <c r="A36" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>99</v>
+      </c>
       <c r="D36" s="12"/>
       <c r="E36" s="16"/>
       <c r="F36" s="13"/>
       <c r="G36" s="17"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35"/>
+      <c r="H36" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I36" s="31"/>
+      <c r="J36" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="31"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
+      <c r="S36" s="31"/>
+      <c r="T36" s="31"/>
     </row>
     <row r="37" spans="1:20" s="5" customFormat="1">
       <c r="A37" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>151</v>
+      <c r="B37" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="16"/>
@@ -2478,108 +2451,106 @@
       <c r="H37" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="I37" s="35"/>
+      <c r="I37" s="28"/>
       <c r="J37" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K37" s="35"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35"/>
-      <c r="T37" s="35"/>
-    </row>
-    <row r="38" spans="1:20" s="5" customFormat="1">
-      <c r="A38" s="13" t="s">
+      <c r="K37" s="31"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+    </row>
+    <row r="38" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="A38" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="13" t="s">
-        <v>152</v>
+      <c r="B38" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" s="12"/>
+        <v>101</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="E38" s="16"/>
       <c r="F38" s="13"/>
       <c r="G38" s="17"/>
       <c r="H38" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="I38" s="28"/>
+      <c r="I38" s="31" t="s">
+        <v>154</v>
+      </c>
       <c r="J38" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K38" s="35"/>
-      <c r="L38" s="42"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="35"/>
-    </row>
-    <row r="39" spans="1:20" s="5" customFormat="1" ht="31.5">
+      <c r="K38" s="31"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N38" s="31"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="31"/>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+    </row>
+    <row r="39" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A39" s="15" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I39" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="J39" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K39" s="35"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N39" s="35"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="35"/>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-    </row>
-    <row r="40" spans="1:20" s="8" customFormat="1" ht="31.5">
+        <v>155</v>
+      </c>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="I39" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="J39" s="15"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="S39" s="28"/>
+      <c r="T39" s="28"/>
+    </row>
+    <row r="40" spans="1:20" s="8" customFormat="1" ht="47.25">
       <c r="A40" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="28"/>
       <c r="F40" s="15"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="58" t="s">
+      <c r="G40" s="53"/>
+      <c r="H40" s="54" t="s">
         <v>126</v>
       </c>
       <c r="I40" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J40" s="15"/>
       <c r="K40" s="28"/>
@@ -2593,67 +2564,69 @@
       <c r="S40" s="28"/>
       <c r="T40" s="28"/>
     </row>
-    <row r="41" spans="1:20" s="8" customFormat="1" ht="47.25">
-      <c r="A41" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I41" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J41" s="15"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="28"/>
-      <c r="Q41" s="28"/>
-      <c r="R41" s="28"/>
-      <c r="S41" s="28"/>
-      <c r="T41" s="28"/>
+    <row r="41" spans="1:20" s="5" customFormat="1">
+      <c r="A41" s="13"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="38"/>
+      <c r="M41" s="31"/>
+      <c r="N41" s="31"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
+      <c r="S41" s="31"/>
+      <c r="T41" s="31"/>
     </row>
     <row r="42" spans="1:20" s="5" customFormat="1">
-      <c r="A42" s="13"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="12"/>
+      <c r="A42" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>102</v>
+      </c>
       <c r="D42" s="12"/>
       <c r="E42" s="16"/>
       <c r="F42" s="13"/>
       <c r="G42" s="17"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="35"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="35"/>
-      <c r="O42" s="35"/>
-      <c r="P42" s="35"/>
-      <c r="Q42" s="35"/>
-      <c r="R42" s="35"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="35"/>
+      <c r="H42" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" s="28"/>
+      <c r="J42" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K42" s="31"/>
+      <c r="L42" s="38"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
     </row>
     <row r="43" spans="1:20" s="5" customFormat="1">
       <c r="A43" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="16"/>
@@ -2666,104 +2639,102 @@
       <c r="J43" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K43" s="35"/>
-      <c r="L43" s="42"/>
-      <c r="M43" s="35"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="35"/>
-      <c r="P43" s="35"/>
-      <c r="Q43" s="35"/>
-      <c r="R43" s="35"/>
-      <c r="S43" s="35"/>
-      <c r="T43" s="35"/>
-    </row>
-    <row r="44" spans="1:20" s="5" customFormat="1">
+      <c r="K43" s="31"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+    </row>
+    <row r="44" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A44" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="12"/>
+        <v>104</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="E44" s="16"/>
       <c r="F44" s="13"/>
       <c r="G44" s="17"/>
       <c r="H44" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="I44" s="28"/>
+      <c r="I44" s="31" t="s">
+        <v>162</v>
+      </c>
       <c r="J44" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="K44" s="35"/>
-      <c r="L44" s="42"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-    </row>
-    <row r="45" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A45" s="13" t="s">
-        <v>15</v>
+      <c r="K44" s="31"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N44" s="31"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="31"/>
+      <c r="S44" s="31"/>
+      <c r="T44" s="31"/>
+    </row>
+    <row r="45" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A45" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I45" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="K45" s="35"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N45" s="35"/>
-      <c r="O45" s="35"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
+        <v>163</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="I45" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="J45" s="15"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28"/>
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28"/>
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
     </row>
     <row r="46" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A46" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
       <c r="E46" s="28"/>
       <c r="F46" s="15"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="58" t="s">
+      <c r="G46" s="53"/>
+      <c r="H46" s="54" t="s">
         <v>126</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J46" s="15"/>
       <c r="K46" s="28"/>
@@ -2777,24 +2748,16 @@
       <c r="S46" s="28"/>
       <c r="T46" s="28"/>
     </row>
-    <row r="47" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A47" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>165</v>
-      </c>
+    <row r="47" spans="1:20" s="8" customFormat="1">
+      <c r="A47" s="15"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
       <c r="E47" s="28"/>
       <c r="F47" s="15"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="I47" s="28" t="s">
-        <v>166</v>
-      </c>
+      <c r="G47" s="53"/>
+      <c r="H47" s="54"/>
+      <c r="I47" s="28"/>
       <c r="J47" s="15"/>
       <c r="K47" s="28"/>
       <c r="L47" s="28"/>
@@ -2807,17 +2770,27 @@
       <c r="S47" s="28"/>
       <c r="T47" s="28"/>
     </row>
-    <row r="48" spans="1:20" s="8" customFormat="1">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="11"/>
+    <row r="48" spans="1:20" s="8" customFormat="1" ht="31.5">
+      <c r="A48" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>70</v>
+      </c>
       <c r="D48" s="11"/>
       <c r="E48" s="28"/>
       <c r="F48" s="15"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="58"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="28" t="s">
+        <v>134</v>
+      </c>
       <c r="I48" s="28"/>
-      <c r="J48" s="15"/>
+      <c r="J48" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="K48" s="28"/>
       <c r="L48" s="28"/>
       <c r="M48" s="28"/>
@@ -2829,22 +2802,22 @@
       <c r="S48" s="28"/>
       <c r="T48" s="28"/>
     </row>
-    <row r="49" spans="1:20" s="8" customFormat="1" ht="31.5">
+    <row r="49" spans="1:20" s="8" customFormat="1">
       <c r="A49" s="15" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D49" s="11"/>
       <c r="E49" s="28"/>
       <c r="F49" s="15"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="28" t="s">
-        <v>134</v>
+      <c r="G49" s="53"/>
+      <c r="H49" s="54" t="s">
+        <v>169</v>
       </c>
       <c r="I49" s="28"/>
       <c r="J49" s="15" t="s">
@@ -2861,21 +2834,21 @@
       <c r="S49" s="28"/>
       <c r="T49" s="28"/>
     </row>
-    <row r="50" spans="1:20" s="8" customFormat="1">
+    <row r="50" spans="1:20" s="8" customFormat="1" ht="31.5">
       <c r="A50" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="28"/>
       <c r="F50" s="15"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="58" t="s">
+      <c r="G50" s="53"/>
+      <c r="H50" s="54" t="s">
         <v>169</v>
       </c>
       <c r="I50" s="28"/>
@@ -2898,16 +2871,16 @@
         <v>15</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D51" s="11"/>
       <c r="E51" s="28"/>
       <c r="F51" s="15"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="58" t="s">
+      <c r="G51" s="53"/>
+      <c r="H51" s="54" t="s">
         <v>169</v>
       </c>
       <c r="I51" s="28"/>
@@ -2930,25 +2903,31 @@
         <v>15</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="D52" s="11"/>
+        <v>184</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="E52" s="28"/>
       <c r="F52" s="15"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="58" t="s">
+      <c r="G52" s="53"/>
+      <c r="H52" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="I52" s="28"/>
+      <c r="I52" s="28" t="s">
+        <v>185</v>
+      </c>
       <c r="J52" s="15" t="s">
         <v>12</v>
       </c>
       <c r="K52" s="28"/>
       <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
+      <c r="M52" s="28" t="s">
+        <v>12</v>
+      </c>
       <c r="N52" s="28"/>
       <c r="O52" s="28"/>
       <c r="P52" s="28"/>
@@ -2957,325 +2936,287 @@
       <c r="S52" s="28"/>
       <c r="T52" s="28"/>
     </row>
-    <row r="53" spans="1:20" s="8" customFormat="1" ht="31.5">
-      <c r="A53" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E53" s="28"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="I53" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="J53" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K53" s="28"/>
-      <c r="L53" s="28"/>
-      <c r="M53" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="28"/>
-      <c r="Q53" s="28"/>
-      <c r="R53" s="28"/>
-      <c r="S53" s="28"/>
-      <c r="T53" s="28"/>
+    <row r="53" spans="1:20" s="5" customFormat="1">
+      <c r="A53" s="13"/>
+      <c r="B53" s="15"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="13"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="31"/>
+      <c r="P53" s="31"/>
+      <c r="Q53" s="31"/>
+      <c r="R53" s="31"/>
+      <c r="S53" s="31"/>
+      <c r="T53" s="31"/>
     </row>
     <row r="54" spans="1:20" s="5" customFormat="1">
-      <c r="A54" s="13"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="11"/>
+      <c r="A54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="D54" s="12"/>
       <c r="E54" s="16"/>
       <c r="F54" s="13"/>
       <c r="G54" s="17"/>
-      <c r="H54" s="16"/>
+      <c r="H54" s="54" t="s">
+        <v>173</v>
+      </c>
       <c r="I54" s="16"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="35"/>
-      <c r="L54" s="42"/>
-      <c r="M54" s="35"/>
-      <c r="N54" s="35"/>
-      <c r="O54" s="35"/>
-      <c r="P54" s="35"/>
-      <c r="Q54" s="35"/>
-      <c r="R54" s="35"/>
-      <c r="S54" s="35"/>
-      <c r="T54" s="35"/>
-    </row>
-    <row r="55" spans="1:20" s="5" customFormat="1">
+      <c r="J54" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K54" s="31"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="31"/>
+      <c r="R54" s="31"/>
+      <c r="S54" s="31"/>
+      <c r="T54" s="31"/>
+    </row>
+    <row r="55" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A55" s="13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="16"/>
       <c r="F55" s="13"/>
       <c r="G55" s="17"/>
-      <c r="H55" s="58" t="s">
+      <c r="H55" s="54" t="s">
         <v>173</v>
       </c>
       <c r="I55" s="16"/>
       <c r="J55" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K55" s="35"/>
-      <c r="L55" s="42"/>
-      <c r="M55" s="35"/>
-      <c r="N55" s="35"/>
-      <c r="O55" s="35"/>
-      <c r="P55" s="35"/>
-      <c r="Q55" s="35"/>
-      <c r="R55" s="35"/>
-      <c r="S55" s="35"/>
-      <c r="T55" s="35"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="38"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="31"/>
     </row>
     <row r="56" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A56" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="16"/>
       <c r="F56" s="13"/>
       <c r="G56" s="17"/>
-      <c r="H56" s="58" t="s">
+      <c r="H56" s="54" t="s">
         <v>173</v>
       </c>
       <c r="I56" s="16"/>
       <c r="J56" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K56" s="35"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="35"/>
-      <c r="N56" s="35"/>
-      <c r="O56" s="35"/>
-      <c r="P56" s="35"/>
-      <c r="Q56" s="35"/>
-      <c r="R56" s="35"/>
-      <c r="S56" s="35"/>
-      <c r="T56" s="35"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="38"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="31"/>
+      <c r="O56" s="31"/>
+      <c r="P56" s="31"/>
+      <c r="Q56" s="31"/>
+      <c r="R56" s="31"/>
+      <c r="S56" s="31"/>
+      <c r="T56" s="31"/>
     </row>
     <row r="57" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A57" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D57" s="12"/>
+        <v>189</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>47</v>
+      </c>
       <c r="E57" s="16"/>
       <c r="F57" s="13"/>
       <c r="G57" s="17"/>
-      <c r="H57" s="58" t="s">
+      <c r="H57" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="I57" s="16"/>
+      <c r="I57" s="28" t="s">
+        <v>190</v>
+      </c>
       <c r="J57" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K57" s="35"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="35"/>
-      <c r="N57" s="35"/>
-      <c r="O57" s="35"/>
-      <c r="P57" s="35"/>
-      <c r="Q57" s="35"/>
-      <c r="R57" s="35"/>
-      <c r="S57" s="35"/>
-      <c r="T57" s="35"/>
-    </row>
-    <row r="58" spans="1:20" s="5" customFormat="1" ht="31.5">
-      <c r="A58" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>47</v>
-      </c>
+      <c r="K57" s="31"/>
+      <c r="L57" s="38"/>
+      <c r="M57" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="31"/>
+      <c r="T57" s="31"/>
+    </row>
+    <row r="58" spans="1:20" s="5" customFormat="1">
+      <c r="A58" s="13"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="12"/>
       <c r="E58" s="16"/>
       <c r="F58" s="13"/>
       <c r="G58" s="17"/>
-      <c r="H58" s="58" t="s">
-        <v>173</v>
-      </c>
-      <c r="I58" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="J58" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="K58" s="35"/>
-      <c r="L58" s="42"/>
-      <c r="M58" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N58" s="35"/>
-      <c r="O58" s="35"/>
-      <c r="P58" s="35"/>
-      <c r="Q58" s="35"/>
-      <c r="R58" s="35"/>
-      <c r="S58" s="35"/>
-      <c r="T58" s="35"/>
-    </row>
-    <row r="59" spans="1:20" s="5" customFormat="1">
-      <c r="A59" s="13"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="17"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="38"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="31"/>
+      <c r="T58" s="31"/>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="D59" s="57"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="57"/>
       <c r="H59" s="16"/>
-      <c r="I59" s="16"/>
+      <c r="I59" s="58"/>
       <c r="J59" s="13"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="42"/>
-      <c r="M59" s="35"/>
-      <c r="N59" s="35"/>
-      <c r="O59" s="35"/>
-      <c r="P59" s="35"/>
-      <c r="Q59" s="35"/>
-      <c r="R59" s="35"/>
-      <c r="S59" s="35"/>
-      <c r="T59" s="35"/>
+      <c r="K59" s="58"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="58"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="58"/>
+      <c r="R59" s="58"/>
+      <c r="S59" s="58"/>
+      <c r="T59" s="58"/>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="C60" s="60" t="s">
-        <v>105</v>
-      </c>
-      <c r="D60" s="61"/>
-      <c r="E60" s="62"/>
-      <c r="F60" s="59"/>
-      <c r="G60" s="61"/>
+        <v>59</v>
+      </c>
+      <c r="B60" s="55"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="57"/>
       <c r="H60" s="16"/>
-      <c r="I60" s="62"/>
+      <c r="I60" s="58"/>
       <c r="J60" s="13"/>
-      <c r="K60" s="62"/>
-      <c r="L60" s="62"/>
-      <c r="M60" s="62"/>
-      <c r="N60" s="62"/>
-      <c r="O60" s="62"/>
-      <c r="P60" s="62"/>
-      <c r="Q60" s="62"/>
-      <c r="R60" s="62"/>
-      <c r="S60" s="62"/>
-      <c r="T60" s="62"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="63"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="62"/>
-      <c r="F61" s="59"/>
-      <c r="G61" s="61"/>
+        <v>16</v>
+      </c>
+      <c r="B61" s="55" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" s="59"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="55"/>
+      <c r="G61" s="57"/>
       <c r="H61" s="16"/>
-      <c r="I61" s="62"/>
+      <c r="I61" s="58"/>
       <c r="J61" s="13"/>
-      <c r="K61" s="62"/>
-      <c r="L61" s="62"/>
-      <c r="M61" s="62"/>
-      <c r="N61" s="62"/>
-      <c r="O61" s="62"/>
-      <c r="P61" s="62"/>
-      <c r="Q61" s="62"/>
-      <c r="R61" s="62"/>
-      <c r="S61" s="62"/>
-      <c r="T61" s="62"/>
+      <c r="K61" s="58"/>
+      <c r="L61" s="58"/>
+      <c r="M61" s="58"/>
+      <c r="N61" s="58"/>
+      <c r="O61" s="58"/>
+      <c r="P61" s="58"/>
+      <c r="Q61" s="58"/>
+      <c r="R61" s="58"/>
+      <c r="S61" s="58"/>
+      <c r="T61" s="58"/>
     </row>
     <row r="62" spans="1:20">
-      <c r="A62" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B62" s="59" t="s">
-        <v>177</v>
-      </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="62"/>
-      <c r="F62" s="59"/>
-      <c r="G62" s="61"/>
+      <c r="A62" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C62" s="59"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="55"/>
+      <c r="G62" s="57"/>
       <c r="H62" s="16"/>
-      <c r="I62" s="62"/>
+      <c r="I62" s="58"/>
       <c r="J62" s="13"/>
-      <c r="K62" s="62"/>
-      <c r="L62" s="62"/>
-      <c r="M62" s="62"/>
-      <c r="N62" s="62"/>
-      <c r="O62" s="62"/>
-      <c r="P62" s="62"/>
-      <c r="Q62" s="62"/>
-      <c r="R62" s="62"/>
-      <c r="S62" s="62"/>
-      <c r="T62" s="62"/>
-    </row>
-    <row r="63" spans="1:20">
-      <c r="A63" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="B63" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" s="63"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="62"/>
-      <c r="F63" s="59"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="16"/>
-      <c r="I63" s="62"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="62"/>
-      <c r="L63" s="62"/>
-      <c r="M63" s="62"/>
-      <c r="N63" s="62"/>
-      <c r="O63" s="62"/>
-      <c r="P63" s="62"/>
-      <c r="Q63" s="62"/>
-      <c r="R63" s="62"/>
-      <c r="S63" s="62"/>
-      <c r="T63" s="62"/>
+      <c r="K62" s="58"/>
+      <c r="L62" s="58"/>
+      <c r="M62" s="58"/>
+      <c r="N62" s="58"/>
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
+      <c r="S62" s="58"/>
+      <c r="T62" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3483,29 +3424,29 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="60"/>
+      <c r="E20" s="22"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="60" t="s">
+        <v>192</v>
+      </c>
+      <c r="B21" s="60" t="s">
         <v>195</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="C21" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="22"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="64" t="s">
-        <v>195</v>
-      </c>
-      <c r="B21" s="64" t="s">
-        <v>198</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D21" s="64"/>
+      <c r="D21" s="60"/>
       <c r="E21" s="22"/>
     </row>
   </sheetData>
@@ -3536,10 +3477,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>

--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_4_qualite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD580D5D-DFF8-4D92-8C3A-4C409869360B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90077F97-14A3-43D8-910B-A461A3246337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -1662,10 +1662,10 @@
         <v>102</v>
       </c>
       <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30" t="s">
+      <c r="Q5" s="30" t="s">
         <v>118</v>
       </c>
+      <c r="R5" s="30"/>
       <c r="S5" s="30"/>
       <c r="T5" s="30"/>
     </row>
